--- a/Allegheny_NonMajority_Local.xlsx
+++ b/Allegheny_NonMajority_Local.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="163">
   <si>
     <t>Year</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Supervisor North Fayette</t>
   </si>
   <si>
-    <t>Commissioner East Deer Ward 2</t>
-  </si>
-  <si>
     <t>JANE BRAUNLICH</t>
   </si>
   <si>
@@ -119,12 +116,6 @@
     <t>REP JEFFREY KAMMERDEINER</t>
   </si>
   <si>
-    <t>ALEXANDER JAMES GIGLER</t>
-  </si>
-  <si>
-    <t>ED KISSEL</t>
-  </si>
-  <si>
     <t>Allegheny County (Pittsburgh + boroughs)</t>
   </si>
   <si>
@@ -161,9 +152,6 @@
     <t>REP Magisterial District Judge 05-02-25</t>
   </si>
   <si>
-    <t>DEM Commissioner Ross Ward 8</t>
-  </si>
-  <si>
     <t>DEM Magisterial District Judge 05-02-04</t>
   </si>
   <si>
@@ -312,12 +300,6 @@
   </si>
   <si>
     <t>CARRIE WHITE</t>
-  </si>
-  <si>
-    <t>DENISE RICKENBRODE</t>
-  </si>
-  <si>
-    <t>LAUREN HERGERT</t>
   </si>
   <si>
     <t>MATTHEW RUDZKI</t>
@@ -879,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -910,7 +892,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>1814</v>
@@ -919,7 +901,7 @@
         <v>41.98102291136311</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -930,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>1263</v>
@@ -939,7 +921,7 @@
         <v>29.22934505901412</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -950,7 +932,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>637</v>
@@ -959,7 +941,7 @@
         <v>14.74195788012034</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -970,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>607</v>
@@ -979,7 +961,7 @@
         <v>14.04767414950243</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -990,7 +972,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>3272</v>
@@ -999,7 +981,7 @@
         <v>41.11585825584317</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1010,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>2246</v>
@@ -1019,7 +1001,7 @@
         <v>28.22317165116863</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1030,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>2068</v>
@@ -1039,7 +1021,7 @@
         <v>25.98642875094245</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1050,7 +1032,7 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10">
         <v>372</v>
@@ -1059,7 +1041,7 @@
         <v>4.674541342045741</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1070,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12">
         <v>333</v>
@@ -1079,7 +1061,7 @@
         <v>41.67709637046308</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1090,7 +1072,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13">
         <v>244</v>
@@ -1099,7 +1081,7 @@
         <v>30.53817271589487</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1110,7 +1092,7 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14">
         <v>222</v>
@@ -1119,7 +1101,7 @@
         <v>27.78473091364205</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1130,7 +1112,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>4417</v>
@@ -1139,7 +1121,7 @@
         <v>45.88137529863924</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1150,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>2712</v>
@@ -1159,7 +1141,7 @@
         <v>28.17076971019009</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1170,7 +1152,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>2498</v>
@@ -1179,7 +1161,7 @@
         <v>25.94785499117067</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1190,7 +1172,7 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20">
         <v>3371</v>
@@ -1199,7 +1181,7 @@
         <v>27.79747670487343</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1210,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21">
         <v>3343</v>
@@ -1219,7 +1201,7 @@
         <v>27.56658695472912</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1230,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2709</v>
@@ -1239,7 +1221,7 @@
         <v>22.33858332646161</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1250,7 +1232,7 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>2704</v>
@@ -1259,7 +1241,7 @@
         <v>22.29735301393584</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1270,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D25">
         <v>2175</v>
@@ -1279,7 +1261,7 @@
         <v>43.20619785458879</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1290,7 +1272,7 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>1500</v>
@@ -1299,7 +1281,7 @@
         <v>29.79737783075089</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1310,7 +1292,7 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>1359</v>
@@ -1319,47 +1301,7 @@
         <v>26.99642431466031</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>2025</v>
-      </c>
-      <c r="B29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29">
-        <v>131</v>
-      </c>
-      <c r="E29">
-        <v>50</v>
-      </c>
-      <c r="F29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>2025</v>
-      </c>
-      <c r="B30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30">
-        <v>131</v>
-      </c>
-      <c r="E30">
-        <v>50</v>
-      </c>
-      <c r="F30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1397,10 +1339,10 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2">
         <v>868</v>
@@ -1409,7 +1351,7 @@
         <v>35.25588952071487</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1417,10 +1359,10 @@
         <v>2017</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>574</v>
@@ -1429,7 +1371,7 @@
         <v>23.31437855402112</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1437,10 +1379,10 @@
         <v>2017</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D4">
         <v>439</v>
@@ -1449,7 +1391,7 @@
         <v>17.83103168155971</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1457,10 +1399,10 @@
         <v>2017</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D5">
         <v>298</v>
@@ -1469,7 +1411,7 @@
         <v>12.10398050365557</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1477,10 +1419,10 @@
         <v>2017</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D6">
         <v>186</v>
@@ -1489,7 +1431,7 @@
         <v>7.554833468724614</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1497,10 +1439,10 @@
         <v>2017</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>97</v>
@@ -1509,7 +1451,7 @@
         <v>3.939886271324126</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1517,10 +1459,10 @@
         <v>2017</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>3586</v>
@@ -1529,7 +1471,7 @@
         <v>41.50943396226415</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1537,10 +1479,10 @@
         <v>2017</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D10">
         <v>2299</v>
@@ -1549,7 +1491,7 @@
         <v>26.61187637458039</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1557,10 +1499,10 @@
         <v>2017</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D11">
         <v>2108</v>
@@ -1569,7 +1511,7 @@
         <v>24.40097233476097</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1577,10 +1519,10 @@
         <v>2017</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D12">
         <v>646</v>
@@ -1589,7 +1531,7 @@
         <v>7.47771732839449</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1597,10 +1539,10 @@
         <v>2017</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D14">
         <v>432</v>
@@ -1609,7 +1551,7 @@
         <v>47.16157205240174</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1617,10 +1559,10 @@
         <v>2017</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D15">
         <v>327</v>
@@ -1629,7 +1571,7 @@
         <v>35.69868995633188</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1637,10 +1579,10 @@
         <v>2017</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16">
         <v>157</v>
@@ -1649,7 +1591,7 @@
         <v>17.13973799126638</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1657,10 +1599,10 @@
         <v>2017</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D18">
         <v>255</v>
@@ -1669,7 +1611,7 @@
         <v>46.02888086642599</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1677,10 +1619,10 @@
         <v>2017</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D19">
         <v>223</v>
@@ -1689,7 +1631,7 @@
         <v>40.25270758122744</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1697,10 +1639,10 @@
         <v>2017</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <v>76</v>
@@ -1709,7 +1651,7 @@
         <v>13.71841155234657</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1717,10 +1659,10 @@
         <v>2017</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D22">
         <v>1169</v>
@@ -1729,7 +1671,7 @@
         <v>43.05709023941068</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1737,10 +1679,10 @@
         <v>2017</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D23">
         <v>1153</v>
@@ -1749,7 +1691,7 @@
         <v>42.46777163904235</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1757,10 +1699,10 @@
         <v>2017</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D24">
         <v>393</v>
@@ -1769,7 +1711,7 @@
         <v>14.47513812154696</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1777,10 +1719,10 @@
         <v>2017</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>279</v>
@@ -1789,7 +1731,7 @@
         <v>47.20812182741117</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1797,10 +1739,10 @@
         <v>2017</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D27">
         <v>177</v>
@@ -1809,7 +1751,7 @@
         <v>29.94923857868021</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1817,10 +1759,10 @@
         <v>2017</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D28">
         <v>135</v>
@@ -1829,7 +1771,7 @@
         <v>22.84263959390863</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1837,10 +1779,10 @@
         <v>2019</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D30">
         <v>1183</v>
@@ -1849,7 +1791,7 @@
         <v>45.57010785824345</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1857,10 +1799,10 @@
         <v>2019</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D31">
         <v>843</v>
@@ -1869,7 +1811,7 @@
         <v>32.47303543913713</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1877,10 +1819,10 @@
         <v>2019</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D32">
         <v>570</v>
@@ -1889,7 +1831,7 @@
         <v>21.95685670261942</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1897,10 +1839,10 @@
         <v>2019</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D34">
         <v>2049</v>
@@ -1909,7 +1851,7 @@
         <v>39.18531267928858</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1917,10 +1859,10 @@
         <v>2019</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D35">
         <v>1518</v>
@@ -1929,7 +1871,7 @@
         <v>29.03040734366036</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1937,10 +1879,10 @@
         <v>2019</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D36">
         <v>822</v>
@@ -1949,7 +1891,7 @@
         <v>15.72002294893861</v>
       </c>
       <c r="F36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1957,10 +1899,10 @@
         <v>2019</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D37">
         <v>702</v>
@@ -1969,7 +1911,7 @@
         <v>13.42512908777969</v>
       </c>
       <c r="F37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1977,10 +1919,10 @@
         <v>2019</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D38">
         <v>138</v>
@@ -1989,7 +1931,7 @@
         <v>2.63912794033276</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1997,10 +1939,10 @@
         <v>2019</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D40">
         <v>1887</v>
@@ -2009,7 +1951,7 @@
         <v>33.847533632287</v>
       </c>
       <c r="F40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2017,10 +1959,10 @@
         <v>2019</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D41">
         <v>1488</v>
@@ -2029,7 +1971,7 @@
         <v>26.69058295964126</v>
       </c>
       <c r="F41" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2037,10 +1979,10 @@
         <v>2019</v>
       </c>
       <c r="B42" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D42">
         <v>1221</v>
@@ -2049,7 +1991,7 @@
         <v>21.90134529147982</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2057,10 +1999,10 @@
         <v>2019</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D43">
         <v>979</v>
@@ -2069,7 +2011,7 @@
         <v>17.56053811659193</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2077,10 +2019,10 @@
         <v>2019</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D45">
         <v>121</v>
@@ -2089,7 +2031,7 @@
         <v>44.48529411764706</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2097,10 +2039,10 @@
         <v>2019</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46">
         <v>81</v>
@@ -2109,7 +2051,7 @@
         <v>29.77941176470588</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2117,10 +2059,10 @@
         <v>2019</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D47">
         <v>70</v>
@@ -2129,7 +2071,7 @@
         <v>25.73529411764706</v>
       </c>
       <c r="F47" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2137,10 +2079,10 @@
         <v>2019</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C49" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D49">
         <v>695</v>
@@ -2149,7 +2091,7 @@
         <v>41.69166166766647</v>
       </c>
       <c r="F49" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2157,10 +2099,10 @@
         <v>2019</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C50" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D50">
         <v>571</v>
@@ -2169,7 +2111,7 @@
         <v>34.25314937012597</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2177,10 +2119,10 @@
         <v>2019</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D51">
         <v>401</v>
@@ -2189,7 +2131,7 @@
         <v>24.05518896220756</v>
       </c>
       <c r="F51" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2197,19 +2139,19 @@
         <v>2021</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D53">
-        <v>235</v>
+        <v>1672</v>
       </c>
       <c r="E53">
-        <v>50</v>
+        <v>36.12791702679343</v>
       </c>
       <c r="F53" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2217,19 +2159,39 @@
         <v>2021</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D54">
-        <v>235</v>
+        <v>1636</v>
       </c>
       <c r="E54">
-        <v>50</v>
+        <v>35.35004321521176</v>
       </c>
       <c r="F54" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>2021</v>
+      </c>
+      <c r="B55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55">
+        <v>634</v>
+      </c>
+      <c r="E55">
+        <v>13.69922212618842</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2237,19 +2199,19 @@
         <v>2021</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D56">
-        <v>1672</v>
+        <v>424</v>
       </c>
       <c r="E56">
-        <v>36.12791702679343</v>
+        <v>9.161624891961971</v>
       </c>
       <c r="F56" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2257,39 +2219,19 @@
         <v>2021</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D57">
-        <v>1636</v>
+        <v>262</v>
       </c>
       <c r="E57">
-        <v>35.35004321521176</v>
+        <v>5.661192739844425</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>2021</v>
-      </c>
-      <c r="B58" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58">
-        <v>634</v>
-      </c>
-      <c r="E58">
-        <v>13.69922212618842</v>
-      </c>
-      <c r="F58" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2297,19 +2239,19 @@
         <v>2021</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D59">
-        <v>424</v>
+        <v>2979</v>
       </c>
       <c r="E59">
-        <v>9.161624891961971</v>
+        <v>41.2318339100346</v>
       </c>
       <c r="F59" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2317,19 +2259,39 @@
         <v>2021</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D60">
-        <v>262</v>
+        <v>2665</v>
       </c>
       <c r="E60">
-        <v>5.661192739844425</v>
+        <v>36.88581314878893</v>
       </c>
       <c r="F60" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61">
+        <v>2021</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61">
+        <v>616</v>
+      </c>
+      <c r="E61">
+        <v>8.525951557093425</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2337,19 +2299,19 @@
         <v>2021</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D62">
-        <v>2979</v>
+        <v>513</v>
       </c>
       <c r="E62">
-        <v>41.2318339100346</v>
+        <v>7.100346020761246</v>
       </c>
       <c r="F62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2357,39 +2319,19 @@
         <v>2021</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D63">
-        <v>2665</v>
+        <v>452</v>
       </c>
       <c r="E63">
-        <v>36.88581314878893</v>
+        <v>6.256055363321799</v>
       </c>
       <c r="F63" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>2021</v>
-      </c>
-      <c r="B64" t="s">
-        <v>50</v>
-      </c>
-      <c r="C64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D64">
-        <v>616</v>
-      </c>
-      <c r="E64">
-        <v>8.525951557093425</v>
-      </c>
-      <c r="F64" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2397,19 +2339,19 @@
         <v>2021</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D65">
-        <v>513</v>
+        <v>1429</v>
       </c>
       <c r="E65">
-        <v>7.100346020761246</v>
+        <v>35.69822633025231</v>
       </c>
       <c r="F65" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2417,19 +2359,39 @@
         <v>2021</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D66">
-        <v>452</v>
+        <v>999</v>
       </c>
       <c r="E66">
-        <v>6.256055363321799</v>
+        <v>24.95628278790907</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67">
+        <v>2021</v>
+      </c>
+      <c r="B67" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67">
+        <v>649</v>
+      </c>
+      <c r="E67">
+        <v>16.21284036972271</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2437,19 +2399,19 @@
         <v>2021</v>
       </c>
       <c r="B68" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D68">
-        <v>1429</v>
+        <v>423</v>
       </c>
       <c r="E68">
-        <v>35.69822633025231</v>
+        <v>10.56707469397952</v>
       </c>
       <c r="F68" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2457,19 +2419,19 @@
         <v>2021</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D69">
-        <v>999</v>
+        <v>373</v>
       </c>
       <c r="E69">
-        <v>24.95628278790907</v>
+        <v>9.318011491381464</v>
       </c>
       <c r="F69" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2477,39 +2439,19 @@
         <v>2021</v>
       </c>
       <c r="B70" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C70" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D70">
-        <v>649</v>
+        <v>130</v>
       </c>
       <c r="E70">
-        <v>16.21284036972271</v>
+        <v>3.247564326754933</v>
       </c>
       <c r="F70" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>2021</v>
-      </c>
-      <c r="B71" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71">
-        <v>423</v>
-      </c>
-      <c r="E71">
-        <v>10.56707469397952</v>
-      </c>
-      <c r="F71" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2517,19 +2459,19 @@
         <v>2021</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D72">
-        <v>373</v>
+        <v>229</v>
       </c>
       <c r="E72">
-        <v>9.318011491381464</v>
+        <v>39.75694444444444</v>
       </c>
       <c r="F72" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2537,19 +2479,39 @@
         <v>2021</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D73">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="E73">
-        <v>3.247564326754933</v>
+        <v>34.02777777777778</v>
       </c>
       <c r="F73" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74">
+        <v>2021</v>
+      </c>
+      <c r="B74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" t="s">
+        <v>113</v>
+      </c>
+      <c r="D74">
+        <v>82</v>
+      </c>
+      <c r="E74">
+        <v>14.23611111111111</v>
+      </c>
+      <c r="F74" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2557,39 +2519,19 @@
         <v>2021</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D75">
-        <v>229</v>
+        <v>69</v>
       </c>
       <c r="E75">
-        <v>39.75694444444444</v>
+        <v>11.97916666666667</v>
       </c>
       <c r="F75" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>2021</v>
-      </c>
-      <c r="B76" t="s">
-        <v>52</v>
-      </c>
-      <c r="C76" t="s">
-        <v>118</v>
-      </c>
-      <c r="D76">
-        <v>196</v>
-      </c>
-      <c r="E76">
-        <v>34.02777777777778</v>
-      </c>
-      <c r="F76" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2597,19 +2539,19 @@
         <v>2021</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D77">
-        <v>82</v>
+        <v>26479</v>
       </c>
       <c r="E77">
-        <v>14.23611111111111</v>
+        <v>46.44868174083884</v>
       </c>
       <c r="F77" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2617,19 +2559,39 @@
         <v>2021</v>
       </c>
       <c r="B78" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C78" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D78">
-        <v>69</v>
+        <v>22406</v>
       </c>
       <c r="E78">
-        <v>11.97916666666667</v>
+        <v>39.30394512954549</v>
       </c>
       <c r="F78" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79">
+        <v>2021</v>
+      </c>
+      <c r="B79" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79">
+        <v>7442</v>
+      </c>
+      <c r="E79">
+        <v>13.0545371621029</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2637,39 +2599,19 @@
         <v>2021</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D80">
-        <v>26479</v>
+        <v>680</v>
       </c>
       <c r="E80">
-        <v>46.44868174083884</v>
+        <v>1.192835967512762</v>
       </c>
       <c r="F80" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>2021</v>
-      </c>
-      <c r="B81" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" t="s">
-        <v>122</v>
-      </c>
-      <c r="D81">
-        <v>22406</v>
-      </c>
-      <c r="E81">
-        <v>39.30394512954549</v>
-      </c>
-      <c r="F81" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2677,19 +2619,19 @@
         <v>2021</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D82">
-        <v>7442</v>
+        <v>160</v>
       </c>
       <c r="E82">
-        <v>13.0545371621029</v>
+        <v>43.83561643835616</v>
       </c>
       <c r="F82" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2697,39 +2639,39 @@
         <v>2021</v>
       </c>
       <c r="B83" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D83">
-        <v>680</v>
+        <v>144</v>
       </c>
       <c r="E83">
-        <v>1.192835967512762</v>
+        <v>39.45205479452055</v>
       </c>
       <c r="F83" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>2021</v>
-      </c>
-      <c r="B85" t="s">
-        <v>54</v>
-      </c>
-      <c r="C85" t="s">
-        <v>125</v>
-      </c>
-      <c r="D85">
-        <v>160</v>
-      </c>
-      <c r="E85">
-        <v>43.83561643835616</v>
-      </c>
-      <c r="F85" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84">
+        <v>2021</v>
+      </c>
+      <c r="B84" t="s">
+        <v>50</v>
+      </c>
+      <c r="C84" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84">
+        <v>61</v>
+      </c>
+      <c r="E84">
+        <v>16.71232876712329</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -2737,19 +2679,19 @@
         <v>2021</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C86" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D86">
-        <v>144</v>
+        <v>2057</v>
       </c>
       <c r="E86">
-        <v>39.45205479452055</v>
+        <v>39.9961112191328</v>
       </c>
       <c r="F86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -2757,39 +2699,39 @@
         <v>2021</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C87" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D87">
-        <v>61</v>
+        <v>1943</v>
       </c>
       <c r="E87">
-        <v>16.71232876712329</v>
+        <v>37.77950612482987</v>
       </c>
       <c r="F87" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>2021</v>
-      </c>
-      <c r="B89" t="s">
-        <v>55</v>
-      </c>
-      <c r="C89" t="s">
-        <v>128</v>
-      </c>
-      <c r="D89">
-        <v>2057</v>
-      </c>
-      <c r="E89">
-        <v>39.9961112191328</v>
-      </c>
-      <c r="F89" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88">
+        <v>2021</v>
+      </c>
+      <c r="B88" t="s">
+        <v>51</v>
+      </c>
+      <c r="C88" t="s">
+        <v>124</v>
+      </c>
+      <c r="D88">
+        <v>1143</v>
+      </c>
+      <c r="E88">
+        <v>22.22438265603733</v>
+      </c>
+      <c r="F88" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -2797,19 +2739,19 @@
         <v>2021</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C90" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="D90">
-        <v>1943</v>
+        <v>733</v>
       </c>
       <c r="E90">
-        <v>37.77950612482987</v>
+        <v>28.812893081761</v>
       </c>
       <c r="F90" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -2817,19 +2759,39 @@
         <v>2021</v>
       </c>
       <c r="B91" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C91" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="D91">
-        <v>1143</v>
+        <v>627</v>
       </c>
       <c r="E91">
-        <v>22.22438265603733</v>
+        <v>24.64622641509434</v>
       </c>
       <c r="F91" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92">
+        <v>2021</v>
+      </c>
+      <c r="B92" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92" t="s">
+        <v>98</v>
+      </c>
+      <c r="D92">
+        <v>461</v>
+      </c>
+      <c r="E92">
+        <v>18.12106918238994</v>
+      </c>
+      <c r="F92" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2837,19 +2799,19 @@
         <v>2021</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C93" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D93">
-        <v>733</v>
+        <v>392</v>
       </c>
       <c r="E93">
-        <v>28.812893081761</v>
+        <v>15.40880503144654</v>
       </c>
       <c r="F93" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2857,39 +2819,19 @@
         <v>2021</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C94" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D94">
-        <v>627</v>
+        <v>331</v>
       </c>
       <c r="E94">
-        <v>24.64622641509434</v>
+        <v>13.01100628930818</v>
       </c>
       <c r="F94" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>2021</v>
-      </c>
-      <c r="B95" t="s">
-        <v>56</v>
-      </c>
-      <c r="C95" t="s">
-        <v>104</v>
-      </c>
-      <c r="D95">
-        <v>461</v>
-      </c>
-      <c r="E95">
-        <v>18.12106918238994</v>
-      </c>
-      <c r="F95" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -2897,19 +2839,19 @@
         <v>2021</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D96">
-        <v>392</v>
+        <v>836</v>
       </c>
       <c r="E96">
-        <v>15.40880503144654</v>
+        <v>27.81104457751164</v>
       </c>
       <c r="F96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2917,19 +2859,39 @@
         <v>2021</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C97" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D97">
-        <v>331</v>
+        <v>796</v>
       </c>
       <c r="E97">
-        <v>13.01100628930818</v>
+        <v>26.48037258815702</v>
       </c>
       <c r="F97" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98">
+        <v>2021</v>
+      </c>
+      <c r="B98" t="s">
+        <v>53</v>
+      </c>
+      <c r="C98" t="s">
+        <v>101</v>
+      </c>
+      <c r="D98">
+        <v>689</v>
+      </c>
+      <c r="E98">
+        <v>22.9208250166334</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -2937,19 +2899,19 @@
         <v>2021</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D99">
-        <v>836</v>
+        <v>383</v>
       </c>
       <c r="E99">
-        <v>27.81104457751164</v>
+        <v>12.74118429807053</v>
       </c>
       <c r="F99" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -2957,79 +2919,79 @@
         <v>2021</v>
       </c>
       <c r="B100" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D100">
-        <v>796</v>
+        <v>302</v>
       </c>
       <c r="E100">
-        <v>26.48037258815702</v>
+        <v>10.04657351962741</v>
       </c>
       <c r="F100" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>2021</v>
-      </c>
-      <c r="B101" t="s">
-        <v>57</v>
-      </c>
-      <c r="C101" t="s">
-        <v>107</v>
-      </c>
-      <c r="D101">
-        <v>689</v>
-      </c>
-      <c r="E101">
-        <v>22.9208250166334</v>
-      </c>
-      <c r="F101" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D102">
-        <v>383</v>
+        <v>64982</v>
       </c>
       <c r="E102">
-        <v>12.74118429807053</v>
+        <v>37.69257540603248</v>
       </c>
       <c r="F102" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C103" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="D103">
-        <v>302</v>
+        <v>50935</v>
       </c>
       <c r="E103">
-        <v>10.04657351962741</v>
+        <v>29.54466357308585</v>
       </c>
       <c r="F103" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104">
+        <v>2023</v>
+      </c>
+      <c r="B104" t="s">
+        <v>54</v>
+      </c>
+      <c r="C104" t="s">
+        <v>127</v>
+      </c>
+      <c r="D104">
+        <v>34147</v>
+      </c>
+      <c r="E104">
+        <v>19.8068445475638</v>
+      </c>
+      <c r="F104" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3037,19 +2999,19 @@
         <v>2023</v>
       </c>
       <c r="B105" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D105">
-        <v>64982</v>
+        <v>16712</v>
       </c>
       <c r="E105">
-        <v>37.69257540603248</v>
+        <v>9.693735498839908</v>
       </c>
       <c r="F105" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3057,19 +3019,19 @@
         <v>2023</v>
       </c>
       <c r="B106" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D106">
-        <v>50935</v>
+        <v>3663</v>
       </c>
       <c r="E106">
-        <v>29.54466357308585</v>
+        <v>2.124709976798144</v>
       </c>
       <c r="F106" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3077,39 +3039,19 @@
         <v>2023</v>
       </c>
       <c r="B107" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D107">
-        <v>34147</v>
+        <v>1961</v>
       </c>
       <c r="E107">
-        <v>19.8068445475638</v>
+        <v>1.137470997679815</v>
       </c>
       <c r="F107" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>2023</v>
-      </c>
-      <c r="B108" t="s">
-        <v>58</v>
-      </c>
-      <c r="C108" t="s">
-        <v>134</v>
-      </c>
-      <c r="D108">
-        <v>16712</v>
-      </c>
-      <c r="E108">
-        <v>9.693735498839908</v>
-      </c>
-      <c r="F108" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3117,19 +3059,19 @@
         <v>2023</v>
       </c>
       <c r="B109" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D109">
-        <v>3663</v>
+        <v>5184</v>
       </c>
       <c r="E109">
-        <v>2.124709976798144</v>
+        <v>38.58578340156308</v>
       </c>
       <c r="F109" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3137,39 +3079,39 @@
         <v>2023</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D110">
-        <v>1961</v>
+        <v>4450</v>
       </c>
       <c r="E110">
-        <v>1.137470997679815</v>
+        <v>33.12244138444362</v>
       </c>
       <c r="F110" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111">
         <v>2023</v>
       </c>
-      <c r="B112" t="s">
-        <v>59</v>
-      </c>
-      <c r="C112" t="s">
-        <v>137</v>
-      </c>
-      <c r="D112">
-        <v>5184</v>
-      </c>
-      <c r="E112">
-        <v>38.58578340156308</v>
-      </c>
-      <c r="F112" t="s">
-        <v>36</v>
+      <c r="B111" t="s">
+        <v>55</v>
+      </c>
+      <c r="C111" t="s">
+        <v>133</v>
+      </c>
+      <c r="D111">
+        <v>3801</v>
+      </c>
+      <c r="E111">
+        <v>28.2917752139933</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3177,19 +3119,19 @@
         <v>2023</v>
       </c>
       <c r="B113" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D113">
-        <v>4450</v>
+        <v>79045</v>
       </c>
       <c r="E113">
-        <v>33.12244138444362</v>
+        <v>48.81460393135263</v>
       </c>
       <c r="F113" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3197,39 +3139,39 @@
         <v>2023</v>
       </c>
       <c r="B114" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C114" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D114">
-        <v>3801</v>
+        <v>55813</v>
       </c>
       <c r="E114">
-        <v>28.2917752139933</v>
+        <v>34.46757529534549</v>
       </c>
       <c r="F114" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115">
         <v>2023</v>
       </c>
-      <c r="B116" t="s">
-        <v>60</v>
-      </c>
-      <c r="C116" t="s">
-        <v>140</v>
-      </c>
-      <c r="D116">
-        <v>79045</v>
-      </c>
-      <c r="E116">
-        <v>48.81460393135263</v>
-      </c>
-      <c r="F116" t="s">
-        <v>36</v>
+      <c r="B115" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115" t="s">
+        <v>136</v>
+      </c>
+      <c r="D115">
+        <v>27071</v>
+      </c>
+      <c r="E115">
+        <v>16.71782077330188</v>
+      </c>
+      <c r="F115" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3237,19 +3179,19 @@
         <v>2023</v>
       </c>
       <c r="B117" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C117" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D117">
-        <v>55813</v>
+        <v>2479</v>
       </c>
       <c r="E117">
-        <v>34.46757529534549</v>
+        <v>32.21991161944372</v>
       </c>
       <c r="F117" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3257,19 +3199,39 @@
         <v>2023</v>
       </c>
       <c r="B118" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C118" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D118">
-        <v>27071</v>
+        <v>1923</v>
       </c>
       <c r="E118">
-        <v>16.71782077330188</v>
+        <v>24.99350142968547</v>
       </c>
       <c r="F118" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119">
+        <v>2023</v>
+      </c>
+      <c r="B119" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" t="s">
+        <v>139</v>
+      </c>
+      <c r="D119">
+        <v>1485</v>
+      </c>
+      <c r="E119">
+        <v>19.30075383415649</v>
+      </c>
+      <c r="F119" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3277,19 +3239,19 @@
         <v>2023</v>
       </c>
       <c r="B120" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C120" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D120">
-        <v>2479</v>
+        <v>1397</v>
       </c>
       <c r="E120">
-        <v>32.21991161944372</v>
+        <v>18.15700545879906</v>
       </c>
       <c r="F120" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3297,19 +3259,19 @@
         <v>2023</v>
       </c>
       <c r="B121" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C121" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D121">
-        <v>1923</v>
+        <v>331</v>
       </c>
       <c r="E121">
-        <v>24.99350142968547</v>
+        <v>4.302053548219392</v>
       </c>
       <c r="F121" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3317,39 +3279,19 @@
         <v>2023</v>
       </c>
       <c r="B122" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C122" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D122">
-        <v>1485</v>
+        <v>79</v>
       </c>
       <c r="E122">
-        <v>19.30075383415649</v>
+        <v>1.026774109695867</v>
       </c>
       <c r="F122" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>2023</v>
-      </c>
-      <c r="B123" t="s">
-        <v>61</v>
-      </c>
-      <c r="C123" t="s">
-        <v>146</v>
-      </c>
-      <c r="D123">
-        <v>1397</v>
-      </c>
-      <c r="E123">
-        <v>18.15700545879906</v>
-      </c>
-      <c r="F123" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3357,19 +3299,19 @@
         <v>2023</v>
       </c>
       <c r="B124" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C124" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D124">
-        <v>331</v>
+        <v>1575</v>
       </c>
       <c r="E124">
-        <v>4.302053548219392</v>
+        <v>46.36443921106859</v>
       </c>
       <c r="F124" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3377,39 +3319,39 @@
         <v>2023</v>
       </c>
       <c r="B125" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C125" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D125">
-        <v>79</v>
+        <v>1107</v>
       </c>
       <c r="E125">
-        <v>1.026774109695867</v>
+        <v>32.58757727406535</v>
       </c>
       <c r="F125" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126">
         <v>2023</v>
       </c>
-      <c r="B127" t="s">
-        <v>62</v>
-      </c>
-      <c r="C127" t="s">
-        <v>149</v>
-      </c>
-      <c r="D127">
-        <v>1575</v>
-      </c>
-      <c r="E127">
-        <v>46.36443921106859</v>
-      </c>
-      <c r="F127" t="s">
-        <v>36</v>
+      <c r="B126" t="s">
+        <v>58</v>
+      </c>
+      <c r="C126" t="s">
+        <v>145</v>
+      </c>
+      <c r="D126">
+        <v>715</v>
+      </c>
+      <c r="E126">
+        <v>21.04798351486606</v>
+      </c>
+      <c r="F126" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3417,19 +3359,19 @@
         <v>2023</v>
       </c>
       <c r="B128" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C128" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D128">
-        <v>1107</v>
+        <v>2837</v>
       </c>
       <c r="E128">
-        <v>32.58757727406535</v>
+        <v>48.79600963192294</v>
       </c>
       <c r="F128" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3437,39 +3379,39 @@
         <v>2023</v>
       </c>
       <c r="B129" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D129">
-        <v>715</v>
+        <v>1674</v>
       </c>
       <c r="E129">
-        <v>21.04798351486606</v>
+        <v>28.79256965944272</v>
       </c>
       <c r="F129" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130">
         <v>2023</v>
       </c>
-      <c r="B131" t="s">
-        <v>63</v>
-      </c>
-      <c r="C131" t="s">
-        <v>152</v>
-      </c>
-      <c r="D131">
-        <v>2837</v>
-      </c>
-      <c r="E131">
-        <v>48.79600963192294</v>
-      </c>
-      <c r="F131" t="s">
-        <v>36</v>
+      <c r="B130" t="s">
+        <v>59</v>
+      </c>
+      <c r="C130" t="s">
+        <v>148</v>
+      </c>
+      <c r="D130">
+        <v>1303</v>
+      </c>
+      <c r="E130">
+        <v>22.41142070863433</v>
+      </c>
+      <c r="F130" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3477,19 +3419,19 @@
         <v>2023</v>
       </c>
       <c r="B132" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C132" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D132">
-        <v>1674</v>
+        <v>22367</v>
       </c>
       <c r="E132">
-        <v>28.79256965944272</v>
+        <v>48.93025901295065</v>
       </c>
       <c r="F132" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3497,39 +3439,39 @@
         <v>2023</v>
       </c>
       <c r="B133" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C133" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D133">
-        <v>1303</v>
+        <v>12213</v>
       </c>
       <c r="E133">
-        <v>22.41142070863433</v>
+        <v>26.71727336366818</v>
       </c>
       <c r="F133" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134">
         <v>2023</v>
       </c>
-      <c r="B135" t="s">
-        <v>64</v>
-      </c>
-      <c r="C135" t="s">
-        <v>155</v>
-      </c>
-      <c r="D135">
-        <v>22367</v>
-      </c>
-      <c r="E135">
-        <v>48.93025901295065</v>
-      </c>
-      <c r="F135" t="s">
-        <v>36</v>
+      <c r="B134" t="s">
+        <v>60</v>
+      </c>
+      <c r="C134" t="s">
+        <v>151</v>
+      </c>
+      <c r="D134">
+        <v>11132</v>
+      </c>
+      <c r="E134">
+        <v>24.35246762338117</v>
+      </c>
+      <c r="F134" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3537,19 +3479,19 @@
         <v>2023</v>
       </c>
       <c r="B136" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C136" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D136">
-        <v>12213</v>
+        <v>648</v>
       </c>
       <c r="E136">
-        <v>26.71727336366818</v>
+        <v>40.17358958462493</v>
       </c>
       <c r="F136" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -3557,39 +3499,39 @@
         <v>2023</v>
       </c>
       <c r="B137" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C137" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D137">
-        <v>11132</v>
+        <v>630</v>
       </c>
       <c r="E137">
-        <v>24.35246762338117</v>
+        <v>39.05765654060757</v>
       </c>
       <c r="F137" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138">
         <v>2023</v>
       </c>
-      <c r="B139" t="s">
-        <v>65</v>
-      </c>
-      <c r="C139" t="s">
-        <v>158</v>
-      </c>
-      <c r="D139">
-        <v>648</v>
-      </c>
-      <c r="E139">
-        <v>40.17358958462493</v>
-      </c>
-      <c r="F139" t="s">
-        <v>36</v>
+      <c r="B138" t="s">
+        <v>61</v>
+      </c>
+      <c r="C138" t="s">
+        <v>154</v>
+      </c>
+      <c r="D138">
+        <v>335</v>
+      </c>
+      <c r="E138">
+        <v>20.76875387476752</v>
+      </c>
+      <c r="F138" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -3597,19 +3539,19 @@
         <v>2023</v>
       </c>
       <c r="B140" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C140" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D140">
-        <v>630</v>
+        <v>1219</v>
       </c>
       <c r="E140">
-        <v>39.05765654060757</v>
+        <v>42.31169732731691</v>
       </c>
       <c r="F140" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -3617,19 +3559,39 @@
         <v>2023</v>
       </c>
       <c r="B141" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C141" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D141">
-        <v>335</v>
+        <v>823</v>
       </c>
       <c r="E141">
-        <v>20.76875387476752</v>
+        <v>28.56646997570288</v>
       </c>
       <c r="F141" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142">
+        <v>2023</v>
+      </c>
+      <c r="B142" t="s">
+        <v>62</v>
+      </c>
+      <c r="C142" t="s">
+        <v>157</v>
+      </c>
+      <c r="D142">
+        <v>671</v>
+      </c>
+      <c r="E142">
+        <v>23.2905241235682</v>
+      </c>
+      <c r="F142" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -3637,39 +3599,19 @@
         <v>2023</v>
       </c>
       <c r="B143" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C143" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D143">
-        <v>1219</v>
+        <v>168</v>
       </c>
       <c r="E143">
-        <v>42.31169732731691</v>
+        <v>5.83130857341201</v>
       </c>
       <c r="F143" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>2023</v>
-      </c>
-      <c r="B144" t="s">
-        <v>66</v>
-      </c>
-      <c r="C144" t="s">
-        <v>162</v>
-      </c>
-      <c r="D144">
-        <v>823</v>
-      </c>
-      <c r="E144">
-        <v>28.56646997570288</v>
-      </c>
-      <c r="F144" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -3677,19 +3619,19 @@
         <v>2023</v>
       </c>
       <c r="B145" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D145">
-        <v>671</v>
+        <v>984</v>
       </c>
       <c r="E145">
-        <v>23.2905241235682</v>
+        <v>36.51205936920223</v>
       </c>
       <c r="F145" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -3697,19 +3639,39 @@
         <v>2023</v>
       </c>
       <c r="B146" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C146" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D146">
-        <v>168</v>
+        <v>869</v>
       </c>
       <c r="E146">
-        <v>5.83130857341201</v>
+        <v>32.24489795918367</v>
       </c>
       <c r="F146" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147">
+        <v>2023</v>
+      </c>
+      <c r="B147" t="s">
+        <v>63</v>
+      </c>
+      <c r="C147" t="s">
+        <v>143</v>
+      </c>
+      <c r="D147">
+        <v>478</v>
+      </c>
+      <c r="E147">
+        <v>17.73654916512059</v>
+      </c>
+      <c r="F147" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -3717,139 +3679,79 @@
         <v>2023</v>
       </c>
       <c r="B148" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C148" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D148">
-        <v>984</v>
+        <v>364</v>
       </c>
       <c r="E148">
-        <v>36.51205936920223</v>
+        <v>13.50649350649351</v>
       </c>
       <c r="F148" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>2023</v>
-      </c>
-      <c r="B149" t="s">
-        <v>67</v>
-      </c>
-      <c r="C149" t="s">
-        <v>151</v>
-      </c>
-      <c r="D149">
-        <v>869</v>
-      </c>
-      <c r="E149">
-        <v>32.24489795918367</v>
-      </c>
-      <c r="F149" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B150" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C150" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D150">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E150">
-        <v>17.73654916512059</v>
+        <v>48.39044652128764</v>
       </c>
       <c r="F150" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B151" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C151" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D151">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="E151">
-        <v>13.50649350649351</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F151" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152">
         <v>2025</v>
       </c>
-      <c r="B153" t="s">
-        <v>68</v>
-      </c>
-      <c r="C153" t="s">
-        <v>166</v>
-      </c>
-      <c r="D153">
-        <v>466</v>
-      </c>
-      <c r="E153">
-        <v>48.39044652128764</v>
-      </c>
-      <c r="F153" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>2025</v>
-      </c>
-      <c r="B154" t="s">
-        <v>68</v>
-      </c>
-      <c r="C154" t="s">
-        <v>167</v>
-      </c>
-      <c r="D154">
-        <v>321</v>
-      </c>
-      <c r="E154">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="F154" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>2025</v>
-      </c>
-      <c r="B155" t="s">
-        <v>68</v>
-      </c>
-      <c r="C155" t="s">
-        <v>168</v>
-      </c>
-      <c r="D155">
+      <c r="B152" t="s">
+        <v>64</v>
+      </c>
+      <c r="C152" t="s">
+        <v>162</v>
+      </c>
+      <c r="D152">
         <v>176</v>
       </c>
-      <c r="E155">
+      <c r="E152">
         <v>18.27622014537902</v>
       </c>
-      <c r="F155" t="s">
-        <v>36</v>
+      <c r="F152" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
